--- a/diseases/d102/2005-2009.xlsx
+++ b/diseases/d102/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>244</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>4.651090089708853</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>192</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>3.659874168951229</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>92</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>1.753689705955797</v>
       </c>
@@ -2545,9 +2536,6 @@
       <c r="O12" t="n">
         <v>37</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.7052882513083096</v>
       </c>
@@ -3089,9 +3077,6 @@
       <c r="O15" t="n">
         <v>88</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>1.67744232743598</v>
       </c>
@@ -3633,9 +3618,6 @@
       <c r="O18" t="n">
         <v>149</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>2.840214849863193</v>
       </c>
@@ -4177,9 +4159,6 @@
       <c r="O21" t="n">
         <v>229</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>4.365162420259539</v>
       </c>
@@ -4721,9 +4700,6 @@
       <c r="O24" t="n">
         <v>334</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>6.366656106404742</v>
       </c>
@@ -5265,9 +5241,6 @@
       <c r="O27" t="n">
         <v>188</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>3.583626790431412</v>
       </c>
@@ -5809,9 +5782,6 @@
       <c r="O30" t="n">
         <v>251</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>4.784523002118533</v>
       </c>
@@ -6353,9 +6323,6 @@
       <c r="O33" t="n">
         <v>350</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>6.671645620484011</v>
       </c>
@@ -6897,9 +6864,6 @@
       <c r="O36" t="n">
         <v>370</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>7.052882513083097</v>
       </c>
@@ -7441,9 +7405,6 @@
       <c r="O39" t="n">
         <v>423</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>8.032286373226167</v>
       </c>
@@ -7985,9 +7946,6 @@
       <c r="O42" t="n">
         <v>244</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>4.633281028527624</v>
       </c>
@@ -8529,9 +8487,6 @@
       <c r="O45" t="n">
         <v>141</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>2.67742879107539</v>
       </c>
@@ -9073,9 +9028,6 @@
       <c r="O48" t="n">
         <v>58</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>1.101353687109025</v>
       </c>
@@ -9617,9 +9569,6 @@
       <c r="O51" t="n">
         <v>73</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>1.386186537223429</v>
       </c>
@@ -10161,9 +10110,6 @@
       <c r="O54" t="n">
         <v>69</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>1.310231110526254</v>
       </c>
@@ -10705,9 +10651,6 @@
       <c r="O57" t="n">
         <v>85</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>1.614052817314951</v>
       </c>
@@ -11249,9 +11192,6 @@
       <c r="O60" t="n">
         <v>154</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>2.924283927841205</v>
       </c>
@@ -11793,9 +11733,6 @@
       <c r="O63" t="n">
         <v>137</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>2.601473364378215</v>
       </c>
@@ -12337,9 +12274,6 @@
       <c r="O66" t="n">
         <v>116</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>2.202707374218051</v>
       </c>
@@ -12881,9 +12815,6 @@
       <c r="O69" t="n">
         <v>233</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>4.424403605110395</v>
       </c>
@@ -13425,9 +13356,6 @@
       <c r="O72" t="n">
         <v>164</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>3.114172494584141</v>
       </c>
@@ -13969,9 +13897,6 @@
       <c r="O75" t="n">
         <v>345</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>6.523329885737732</v>
       </c>
@@ -14513,9 +14438,6 @@
       <c r="O78" t="n">
         <v>122</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>2.306800713217401</v>
       </c>
@@ -15057,9 +14979,6 @@
       <c r="O81" t="n">
         <v>29</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.5483378744533166</v>
       </c>
@@ -15601,9 +15520,6 @@
       <c r="O84" t="n">
         <v>35</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.661787089857451</v>
       </c>
@@ -16145,9 +16061,6 @@
       <c r="O87" t="n">
         <v>52</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.9832265335024987</v>
       </c>
@@ -16689,9 +16602,6 @@
       <c r="O90" t="n">
         <v>64</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>1.210124964310768</v>
       </c>
@@ -17233,9 +17143,6 @@
       <c r="O93" t="n">
         <v>88</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>1.663921825927306</v>
       </c>
@@ -17777,9 +17684,6 @@
       <c r="O96" t="n">
         <v>124</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>2.344617118352113</v>
       </c>
@@ -18321,9 +18225,6 @@
       <c r="O99" t="n">
         <v>90</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>1.701738231062017</v>
       </c>
@@ -18865,9 +18766,6 @@
       <c r="O102" t="n">
         <v>186</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>3.516925677528168</v>
       </c>
@@ -19409,9 +19307,6 @@
       <c r="O105" t="n">
         <v>268</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>5.06739828805134</v>
       </c>
@@ -19953,9 +19848,6 @@
       <c r="O108" t="n">
         <v>337</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>6.372064265198886</v>
       </c>
@@ -20497,9 +20389,6 @@
       <c r="O111" t="n">
         <v>315</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>5.928433085022952</v>
       </c>
@@ -21041,9 +20930,6 @@
       <c r="O114" t="n">
         <v>146</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>2.747781683851908</v>
       </c>
@@ -21585,9 +21471,6 @@
       <c r="O117" t="n">
         <v>73</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>1.373890841925954</v>
       </c>
@@ -22129,9 +22012,6 @@
       <c r="O120" t="n">
         <v>58</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>1.091584504543909</v>
       </c>
@@ -22673,9 +22553,6 @@
       <c r="O123" t="n">
         <v>60</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>1.129225349528181</v>
       </c>
@@ -23217,9 +23094,6 @@
       <c r="O126" t="n">
         <v>114</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>2.145528164103545</v>
       </c>
@@ -23761,9 +23635,6 @@
       <c r="O129" t="n">
         <v>258</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>4.85566900297118</v>
       </c>
@@ -24453,9 +24324,6 @@
       <c r="O133" t="n">
         <v>378</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>7.114119702027543</v>
       </c>
@@ -25145,9 +25013,6 @@
       <c r="O137" t="n">
         <v>306</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>5.759049282593725</v>
       </c>
@@ -25837,9 +25702,6 @@
       <c r="O141" t="n">
         <v>388</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>7.302323926948906</v>
       </c>
@@ -26529,9 +26391,6 @@
       <c r="O145" t="n">
         <v>496</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>9.334929556099633</v>
       </c>
@@ -27221,9 +27080,6 @@
       <c r="O149" t="n">
         <v>667</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>12.55322180225495</v>
       </c>
@@ -27913,9 +27769,6 @@
       <c r="O153" t="n">
         <v>607</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>11.36947584187738</v>
       </c>
@@ -28605,9 +28458,6 @@
       <c r="O157" t="n">
         <v>311</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>5.825217441225476</v>
       </c>
@@ -29297,9 +29147,6 @@
       <c r="O161" t="n">
         <v>161</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>3.015627035489716</v>
       </c>
@@ -29989,9 +29836,6 @@
       <c r="O165" t="n">
         <v>91</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>1.704484846146361</v>
       </c>
@@ -30681,9 +30525,6 @@
       <c r="O169" t="n">
         <v>107</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>2.004174489424842</v>
       </c>
@@ -31373,9 +31214,6 @@
       <c r="O173" t="n">
         <v>111</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>2.079096900244462</v>
       </c>
@@ -32065,9 +31903,6 @@
       <c r="O177" t="n">
         <v>118</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>2.210211119178798</v>
       </c>
@@ -32757,9 +32592,6 @@
       <c r="O181" t="n">
         <v>133</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>2.491170159752374</v>
       </c>
@@ -33449,9 +33281,6 @@
       <c r="O185" t="n">
         <v>106</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>1.985443886719937</v>
       </c>
@@ -34141,9 +33970,6 @@
       <c r="O189" t="n">
         <v>61</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>1.142566764999209</v>
       </c>
@@ -34833,9 +34659,6 @@
       <c r="O193" t="n">
         <v>46</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.861607724425633</v>
       </c>
@@ -35524,9 +35347,6 @@
       </c>
       <c r="O197" t="n">
         <v>74</v>
-      </c>
-      <c r="Q197" t="n">
-        <v>0</v>
       </c>
       <c r="R197" t="n">
         <v>1.386064600162975</v>
